--- a/data/reports/dedicated_competitors_20260825.xlsx
+++ b/data/reports/dedicated_competitors_20260825.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB197"/>
+  <dimension ref="A1:AB167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>E3-1231v3</t>
+          <t>E3-1230v3</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -650,7 +650,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>E3-1231v3</t>
+          <t>E3-1230v3</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -700,7 +700,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>E3-1231v3</t>
+          <t>E3-1230v3</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>E3-1231v3</t>
+          <t>E3-1230v3</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E3-1231v3</t>
+          <t>E3-1230v3</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -850,7 +850,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>E3-1231v3</t>
+          <t>E3-1230v3</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>E3-1230v5/v6</t>
+          <t>E3-1230v6</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -8568,25 +8568,25 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Silver 4314</t>
+          <t>Silver 4516Y+</t>
         </is>
       </c>
       <c r="C153" t="n">
         <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E153" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2×1000 ГБ NVMe</t>
+          <t>2×480 ГБ SSD + 2×2000 ГБ SSD</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>41968</v>
+        <v>55754</v>
       </c>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
@@ -8618,14 +8618,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Silver 4314</t>
+          <t>Silver 4516Y+</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>2</v>
       </c>
       <c r="D154" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E154" t="n">
         <v>128</v>
@@ -8636,7 +8636,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>43066</v>
+        <v>52780</v>
       </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
@@ -8652,31 +8652,13 @@
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
-      <c r="V154" t="n">
-        <v>51870</v>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>2 x Silver 4314 / 128 / 1N</t>
-        </is>
-      </c>
-      <c r="Z154" t="n">
-        <v>100</v>
-      </c>
+      <c r="V154" t="inlineStr"/>
+      <c r="W154" t="inlineStr"/>
+      <c r="X154" t="inlineStr"/>
+      <c r="Y154" t="inlineStr"/>
+      <c r="Z154" t="inlineStr"/>
       <c r="AA154" t="inlineStr"/>
-      <c r="AB154" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8686,25 +8668,25 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Silver 4314</t>
+          <t>Silver 4516Y+</t>
         </is>
       </c>
       <c r="C155" t="n">
         <v>2</v>
       </c>
       <c r="D155" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E155" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2×480 ГБ SSD + 2×2000 ГБ SSD</t>
+          <t>2×1000 ГБ NVMe</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>47824</v>
+        <v>54656</v>
       </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
@@ -8736,25 +8718,25 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Silver 4314</t>
+          <t>Silver 4516Y+</t>
         </is>
       </c>
       <c r="C156" t="n">
         <v>2</v>
       </c>
       <c r="D156" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E156" t="n">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2×1000 ГБ SSD</t>
+          <t>2×2000 ГБ NVMe</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>44530</v>
+        <v>57706</v>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
@@ -8786,25 +8768,25 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Silver 4314</t>
+          <t>Silver 4516Y+</t>
         </is>
       </c>
       <c r="C157" t="n">
         <v>2</v>
       </c>
       <c r="D157" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E157" t="n">
-        <v>192</v>
+        <v>384</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2×1000 ГБ NVMe</t>
+          <t>2×4000 ГБ NVMe</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>44164</v>
+        <v>63440</v>
       </c>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
@@ -8836,25 +8818,25 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Silver 4314</t>
+          <t>Silver 4516Y+</t>
         </is>
       </c>
       <c r="C158" t="n">
         <v>2</v>
       </c>
       <c r="D158" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E158" t="n">
-        <v>256</v>
+        <v>768</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2×2000 ГБ SSD</t>
+          <t>2×8000 ГБ NVMe</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>48068</v>
+        <v>76128</v>
       </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
@@ -8886,7 +8868,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Silver 4314</t>
+          <t>Gold 6526Y</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -8904,7 +8886,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>49288</v>
+        <v>80866</v>
       </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
@@ -8936,7 +8918,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Silver 4314</t>
+          <t>Gold 6526Y</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -8954,7 +8936,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>56608</v>
+        <v>86620</v>
       </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
@@ -8986,7 +8968,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Silver 4314</t>
+          <t>Gold 6526Y</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -9004,7 +8986,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>65636</v>
+        <v>99308</v>
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -9036,25 +9018,25 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Gold 5317</t>
+          <t>Gold 6530</t>
         </is>
       </c>
       <c r="C162" t="n">
         <v>2</v>
       </c>
       <c r="D162" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E162" t="n">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2×1000 ГБ NVMe</t>
+          <t>2×480 ГБ SSD + 2×2000 ГБ SSD</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>49044</v>
+        <v>60878</v>
       </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
@@ -9086,25 +9068,25 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Gold 5317</t>
+          <t>Gold 6530</t>
         </is>
       </c>
       <c r="C163" t="n">
         <v>2</v>
       </c>
       <c r="D163" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E163" t="n">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2×2000 ГБ NVMe</t>
+          <t>2×1000 ГБ NVMe</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>52094</v>
+        <v>59780</v>
       </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
@@ -9136,25 +9118,25 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Gold 5317</t>
+          <t>Gold 6530</t>
         </is>
       </c>
       <c r="C164" t="n">
         <v>2</v>
       </c>
       <c r="D164" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E164" t="n">
-        <v>384</v>
+        <v>256</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2×4000 ГБ NVMe</t>
+          <t>2×2000 ГБ NVMe</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>57950</v>
+        <v>62830</v>
       </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
@@ -9186,25 +9168,25 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Gold 5320</t>
+          <t>Gold 6530</t>
         </is>
       </c>
       <c r="C165" t="n">
         <v>2</v>
       </c>
       <c r="D165" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E165" t="n">
-        <v>128</v>
+        <v>384</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2×480 ГБ SSD + 2×2000 ГБ SSD</t>
+          <t>2×4000 ГБ NVMe</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>53924</v>
+        <v>68808</v>
       </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
@@ -9236,25 +9218,25 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Gold 5320</t>
+          <t>Gold 6530</t>
         </is>
       </c>
       <c r="C166" t="n">
         <v>2</v>
       </c>
       <c r="D166" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E166" t="n">
-        <v>192</v>
+        <v>768</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2×1000 ГБ NVMe</t>
+          <t>2×8000 ГБ NVMe</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>52948</v>
+        <v>81374</v>
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
@@ -9286,17 +9268,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Gold 5320</t>
+          <t>Gold 6538Y</t>
         </is>
       </c>
       <c r="C167" t="n">
         <v>2</v>
       </c>
       <c r="D167" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E167" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -9304,7 +9286,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>55998</v>
+        <v>116998</v>
       </c>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
@@ -9328,1524 +9310,6 @@
       <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="inlineStr"/>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>MIR-167</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Gold 6326</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>2</v>
-      </c>
-      <c r="D168" t="n">
-        <v>16</v>
-      </c>
-      <c r="E168" t="n">
-        <v>128</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2×480 ГБ SSD + 2×2000 ГБ SSD</t>
-        </is>
-      </c>
-      <c r="G168" t="n">
-        <v>52704</v>
-      </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
-      <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr"/>
-      <c r="T168" t="inlineStr"/>
-      <c r="U168" t="inlineStr"/>
-      <c r="V168" t="inlineStr"/>
-      <c r="W168" t="inlineStr"/>
-      <c r="X168" t="inlineStr"/>
-      <c r="Y168" t="inlineStr"/>
-      <c r="Z168" t="inlineStr"/>
-      <c r="AA168" t="inlineStr"/>
-      <c r="AB168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>MIR-168</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Gold 6326</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>2</v>
-      </c>
-      <c r="D169" t="n">
-        <v>16</v>
-      </c>
-      <c r="E169" t="n">
-        <v>192</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2×1000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G169" t="n">
-        <v>51728</v>
-      </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
-      <c r="T169" t="inlineStr"/>
-      <c r="U169" t="inlineStr"/>
-      <c r="V169" t="inlineStr"/>
-      <c r="W169" t="inlineStr"/>
-      <c r="X169" t="inlineStr"/>
-      <c r="Y169" t="inlineStr"/>
-      <c r="Z169" t="inlineStr"/>
-      <c r="AA169" t="inlineStr"/>
-      <c r="AB169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>MIR-169</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Gold 6326</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
-        <v>2</v>
-      </c>
-      <c r="D170" t="n">
-        <v>16</v>
-      </c>
-      <c r="E170" t="n">
-        <v>256</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2×2000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G170" t="n">
-        <v>54778</v>
-      </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
-      <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr"/>
-      <c r="T170" t="inlineStr"/>
-      <c r="U170" t="inlineStr"/>
-      <c r="V170" t="inlineStr"/>
-      <c r="W170" t="inlineStr"/>
-      <c r="X170" t="inlineStr"/>
-      <c r="Y170" t="inlineStr"/>
-      <c r="Z170" t="inlineStr"/>
-      <c r="AA170" t="inlineStr"/>
-      <c r="AB170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>MIR-170</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Gold 6326</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>2</v>
-      </c>
-      <c r="D171" t="n">
-        <v>16</v>
-      </c>
-      <c r="E171" t="n">
-        <v>384</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2×4000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G171" t="n">
-        <v>60634</v>
-      </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
-      <c r="T171" t="inlineStr"/>
-      <c r="U171" t="inlineStr"/>
-      <c r="V171" t="inlineStr"/>
-      <c r="W171" t="inlineStr"/>
-      <c r="X171" t="inlineStr"/>
-      <c r="Y171" t="inlineStr"/>
-      <c r="Z171" t="inlineStr"/>
-      <c r="AA171" t="inlineStr"/>
-      <c r="AB171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>MIR-171</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Gold 6326</t>
-        </is>
-      </c>
-      <c r="C172" t="n">
-        <v>2</v>
-      </c>
-      <c r="D172" t="n">
-        <v>16</v>
-      </c>
-      <c r="E172" t="n">
-        <v>768</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2×8000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G172" t="n">
-        <v>73200</v>
-      </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
-      <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
-      <c r="T172" t="inlineStr"/>
-      <c r="U172" t="inlineStr"/>
-      <c r="V172" t="inlineStr"/>
-      <c r="W172" t="inlineStr"/>
-      <c r="X172" t="inlineStr"/>
-      <c r="Y172" t="inlineStr"/>
-      <c r="Z172" t="inlineStr"/>
-      <c r="AA172" t="inlineStr"/>
-      <c r="AB172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>MIR-172</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Gold 6338</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>2</v>
-      </c>
-      <c r="D173" t="n">
-        <v>32</v>
-      </c>
-      <c r="E173" t="n">
-        <v>192</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2×1000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G173" t="n">
-        <v>54900</v>
-      </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
-      <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr"/>
-      <c r="T173" t="inlineStr"/>
-      <c r="U173" t="inlineStr"/>
-      <c r="V173" t="inlineStr"/>
-      <c r="W173" t="inlineStr"/>
-      <c r="X173" t="inlineStr"/>
-      <c r="Y173" t="inlineStr"/>
-      <c r="Z173" t="inlineStr"/>
-      <c r="AA173" t="inlineStr"/>
-      <c r="AB173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>MIR-173</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Gold 6338</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
-        <v>2</v>
-      </c>
-      <c r="D174" t="n">
-        <v>32</v>
-      </c>
-      <c r="E174" t="n">
-        <v>256</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2×2000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G174" t="n">
-        <v>57950</v>
-      </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
-      <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
-      <c r="T174" t="inlineStr"/>
-      <c r="U174" t="inlineStr"/>
-      <c r="V174" t="inlineStr"/>
-      <c r="W174" t="inlineStr"/>
-      <c r="X174" t="inlineStr"/>
-      <c r="Y174" t="inlineStr"/>
-      <c r="Z174" t="inlineStr"/>
-      <c r="AA174" t="inlineStr"/>
-      <c r="AB174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>MIR-174</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Gold 6338</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
-        <v>2</v>
-      </c>
-      <c r="D175" t="n">
-        <v>32</v>
-      </c>
-      <c r="E175" t="n">
-        <v>384</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2×4000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G175" t="n">
-        <v>63928</v>
-      </c>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
-      <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr"/>
-      <c r="T175" t="inlineStr"/>
-      <c r="U175" t="inlineStr"/>
-      <c r="V175" t="inlineStr"/>
-      <c r="W175" t="inlineStr"/>
-      <c r="X175" t="inlineStr"/>
-      <c r="Y175" t="inlineStr"/>
-      <c r="Z175" t="inlineStr"/>
-      <c r="AA175" t="inlineStr"/>
-      <c r="AB175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>MIR-175</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Gold 6338</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
-        <v>2</v>
-      </c>
-      <c r="D176" t="n">
-        <v>32</v>
-      </c>
-      <c r="E176" t="n">
-        <v>768</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2×8000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G176" t="n">
-        <v>76494</v>
-      </c>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
-      <c r="T176" t="inlineStr"/>
-      <c r="U176" t="inlineStr"/>
-      <c r="V176" t="inlineStr"/>
-      <c r="W176" t="inlineStr"/>
-      <c r="X176" t="inlineStr"/>
-      <c r="Y176" t="inlineStr"/>
-      <c r="Z176" t="inlineStr"/>
-      <c r="AA176" t="inlineStr"/>
-      <c r="AB176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>MIR-176</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Gold 6348</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
-        <v>2</v>
-      </c>
-      <c r="D177" t="n">
-        <v>28</v>
-      </c>
-      <c r="E177" t="n">
-        <v>128</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2×480 ГБ SSD + 2×2000 ГБ SSD</t>
-        </is>
-      </c>
-      <c r="G177" t="n">
-        <v>59170</v>
-      </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr"/>
-      <c r="T177" t="inlineStr"/>
-      <c r="U177" t="inlineStr"/>
-      <c r="V177" t="inlineStr"/>
-      <c r="W177" t="inlineStr"/>
-      <c r="X177" t="inlineStr"/>
-      <c r="Y177" t="inlineStr"/>
-      <c r="Z177" t="inlineStr"/>
-      <c r="AA177" t="inlineStr"/>
-      <c r="AB177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>MIR-177</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Gold 6348</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>2</v>
-      </c>
-      <c r="D178" t="n">
-        <v>28</v>
-      </c>
-      <c r="E178" t="n">
-        <v>192</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2×1000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G178" t="n">
-        <v>58438</v>
-      </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
-      <c r="T178" t="inlineStr"/>
-      <c r="U178" t="inlineStr"/>
-      <c r="V178" t="inlineStr"/>
-      <c r="W178" t="inlineStr"/>
-      <c r="X178" t="inlineStr"/>
-      <c r="Y178" t="inlineStr"/>
-      <c r="Z178" t="inlineStr"/>
-      <c r="AA178" t="inlineStr"/>
-      <c r="AB178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>MIR-178</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Gold 6348</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>2</v>
-      </c>
-      <c r="D179" t="n">
-        <v>28</v>
-      </c>
-      <c r="E179" t="n">
-        <v>256</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2×2000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G179" t="n">
-        <v>61488</v>
-      </c>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
-      <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr"/>
-      <c r="T179" t="inlineStr"/>
-      <c r="U179" t="inlineStr"/>
-      <c r="V179" t="inlineStr"/>
-      <c r="W179" t="inlineStr"/>
-      <c r="X179" t="inlineStr"/>
-      <c r="Y179" t="inlineStr"/>
-      <c r="Z179" t="inlineStr"/>
-      <c r="AA179" t="inlineStr"/>
-      <c r="AB179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>MIR-179</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Gold 6348</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>2</v>
-      </c>
-      <c r="D180" t="n">
-        <v>28</v>
-      </c>
-      <c r="E180" t="n">
-        <v>384</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2×4000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G180" t="n">
-        <v>67344</v>
-      </c>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
-      <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
-      <c r="T180" t="inlineStr"/>
-      <c r="U180" t="inlineStr"/>
-      <c r="V180" t="inlineStr"/>
-      <c r="W180" t="inlineStr"/>
-      <c r="X180" t="inlineStr"/>
-      <c r="Y180" t="inlineStr"/>
-      <c r="Z180" t="inlineStr"/>
-      <c r="AA180" t="inlineStr"/>
-      <c r="AB180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>MIR-180</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Gold 6348</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>2</v>
-      </c>
-      <c r="D181" t="n">
-        <v>28</v>
-      </c>
-      <c r="E181" t="n">
-        <v>512</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2×8000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G181" t="n">
-        <v>75030</v>
-      </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="n">
-        <v>95900</v>
-      </c>
-      <c r="P181" t="inlineStr">
-        <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="R181" t="inlineStr">
-        <is>
-          <t>RD-55129</t>
-        </is>
-      </c>
-      <c r="S181" t="n">
-        <v>100</v>
-      </c>
-      <c r="T181" t="inlineStr"/>
-      <c r="U181" t="n">
-        <v>1</v>
-      </c>
-      <c r="V181" t="inlineStr"/>
-      <c r="W181" t="inlineStr"/>
-      <c r="X181" t="inlineStr"/>
-      <c r="Y181" t="inlineStr"/>
-      <c r="Z181" t="inlineStr"/>
-      <c r="AA181" t="inlineStr"/>
-      <c r="AB181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>MIR-181</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Gold 6348</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>2</v>
-      </c>
-      <c r="D182" t="n">
-        <v>28</v>
-      </c>
-      <c r="E182" t="n">
-        <v>768</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2×8000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G182" t="n">
-        <v>79788</v>
-      </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
-      <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
-      <c r="T182" t="inlineStr"/>
-      <c r="U182" t="inlineStr"/>
-      <c r="V182" t="inlineStr"/>
-      <c r="W182" t="inlineStr"/>
-      <c r="X182" t="inlineStr"/>
-      <c r="Y182" t="inlineStr"/>
-      <c r="Z182" t="inlineStr"/>
-      <c r="AA182" t="inlineStr"/>
-      <c r="AB182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>MIR-182</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Silver 4516Y+</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
-        <v>2</v>
-      </c>
-      <c r="D183" t="n">
-        <v>24</v>
-      </c>
-      <c r="E183" t="n">
-        <v>128</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2×480 ГБ SSD + 2×2000 ГБ SSD</t>
-        </is>
-      </c>
-      <c r="G183" t="n">
-        <v>55754</v>
-      </c>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
-      <c r="R183" t="inlineStr"/>
-      <c r="S183" t="inlineStr"/>
-      <c r="T183" t="inlineStr"/>
-      <c r="U183" t="inlineStr"/>
-      <c r="V183" t="inlineStr"/>
-      <c r="W183" t="inlineStr"/>
-      <c r="X183" t="inlineStr"/>
-      <c r="Y183" t="inlineStr"/>
-      <c r="Z183" t="inlineStr"/>
-      <c r="AA183" t="inlineStr"/>
-      <c r="AB183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>MIR-183</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Silver 4516Y+</t>
-        </is>
-      </c>
-      <c r="C184" t="n">
-        <v>2</v>
-      </c>
-      <c r="D184" t="n">
-        <v>24</v>
-      </c>
-      <c r="E184" t="n">
-        <v>128</v>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2×1000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G184" t="n">
-        <v>52780</v>
-      </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
-      <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr"/>
-      <c r="T184" t="inlineStr"/>
-      <c r="U184" t="inlineStr"/>
-      <c r="V184" t="inlineStr"/>
-      <c r="W184" t="inlineStr"/>
-      <c r="X184" t="inlineStr"/>
-      <c r="Y184" t="inlineStr"/>
-      <c r="Z184" t="inlineStr"/>
-      <c r="AA184" t="inlineStr"/>
-      <c r="AB184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>MIR-184</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Silver 4516Y+</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>2</v>
-      </c>
-      <c r="D185" t="n">
-        <v>24</v>
-      </c>
-      <c r="E185" t="n">
-        <v>192</v>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2×1000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G185" t="n">
-        <v>54656</v>
-      </c>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
-      <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr"/>
-      <c r="T185" t="inlineStr"/>
-      <c r="U185" t="inlineStr"/>
-      <c r="V185" t="inlineStr"/>
-      <c r="W185" t="inlineStr"/>
-      <c r="X185" t="inlineStr"/>
-      <c r="Y185" t="inlineStr"/>
-      <c r="Z185" t="inlineStr"/>
-      <c r="AA185" t="inlineStr"/>
-      <c r="AB185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>MIR-185</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Silver 4516Y+</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>2</v>
-      </c>
-      <c r="D186" t="n">
-        <v>24</v>
-      </c>
-      <c r="E186" t="n">
-        <v>256</v>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2×2000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G186" t="n">
-        <v>57706</v>
-      </c>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
-      <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
-      <c r="T186" t="inlineStr"/>
-      <c r="U186" t="inlineStr"/>
-      <c r="V186" t="inlineStr"/>
-      <c r="W186" t="inlineStr"/>
-      <c r="X186" t="inlineStr"/>
-      <c r="Y186" t="inlineStr"/>
-      <c r="Z186" t="inlineStr"/>
-      <c r="AA186" t="inlineStr"/>
-      <c r="AB186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>MIR-186</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Silver 4516Y+</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>2</v>
-      </c>
-      <c r="D187" t="n">
-        <v>24</v>
-      </c>
-      <c r="E187" t="n">
-        <v>384</v>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2×4000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G187" t="n">
-        <v>63440</v>
-      </c>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
-      <c r="R187" t="inlineStr"/>
-      <c r="S187" t="inlineStr"/>
-      <c r="T187" t="inlineStr"/>
-      <c r="U187" t="inlineStr"/>
-      <c r="V187" t="inlineStr"/>
-      <c r="W187" t="inlineStr"/>
-      <c r="X187" t="inlineStr"/>
-      <c r="Y187" t="inlineStr"/>
-      <c r="Z187" t="inlineStr"/>
-      <c r="AA187" t="inlineStr"/>
-      <c r="AB187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>MIR-187</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Silver 4516Y+</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>2</v>
-      </c>
-      <c r="D188" t="n">
-        <v>24</v>
-      </c>
-      <c r="E188" t="n">
-        <v>768</v>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2×8000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G188" t="n">
-        <v>76128</v>
-      </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
-      <c r="R188" t="inlineStr"/>
-      <c r="S188" t="inlineStr"/>
-      <c r="T188" t="inlineStr"/>
-      <c r="U188" t="inlineStr"/>
-      <c r="V188" t="inlineStr"/>
-      <c r="W188" t="inlineStr"/>
-      <c r="X188" t="inlineStr"/>
-      <c r="Y188" t="inlineStr"/>
-      <c r="Z188" t="inlineStr"/>
-      <c r="AA188" t="inlineStr"/>
-      <c r="AB188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>MIR-188</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Gold 6526Y</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>2</v>
-      </c>
-      <c r="D189" t="n">
-        <v>16</v>
-      </c>
-      <c r="E189" t="n">
-        <v>256</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2×2000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G189" t="n">
-        <v>80866</v>
-      </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
-      <c r="R189" t="inlineStr"/>
-      <c r="S189" t="inlineStr"/>
-      <c r="T189" t="inlineStr"/>
-      <c r="U189" t="inlineStr"/>
-      <c r="V189" t="inlineStr"/>
-      <c r="W189" t="inlineStr"/>
-      <c r="X189" t="inlineStr"/>
-      <c r="Y189" t="inlineStr"/>
-      <c r="Z189" t="inlineStr"/>
-      <c r="AA189" t="inlineStr"/>
-      <c r="AB189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>MIR-189</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Gold 6526Y</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>2</v>
-      </c>
-      <c r="D190" t="n">
-        <v>16</v>
-      </c>
-      <c r="E190" t="n">
-        <v>384</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2×4000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G190" t="n">
-        <v>86620</v>
-      </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
-      <c r="R190" t="inlineStr"/>
-      <c r="S190" t="inlineStr"/>
-      <c r="T190" t="inlineStr"/>
-      <c r="U190" t="inlineStr"/>
-      <c r="V190" t="inlineStr"/>
-      <c r="W190" t="inlineStr"/>
-      <c r="X190" t="inlineStr"/>
-      <c r="Y190" t="inlineStr"/>
-      <c r="Z190" t="inlineStr"/>
-      <c r="AA190" t="inlineStr"/>
-      <c r="AB190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>MIR-190</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Gold 6526Y</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>2</v>
-      </c>
-      <c r="D191" t="n">
-        <v>16</v>
-      </c>
-      <c r="E191" t="n">
-        <v>768</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2×8000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G191" t="n">
-        <v>99308</v>
-      </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
-      <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
-      <c r="T191" t="inlineStr"/>
-      <c r="U191" t="inlineStr"/>
-      <c r="V191" t="inlineStr"/>
-      <c r="W191" t="inlineStr"/>
-      <c r="X191" t="inlineStr"/>
-      <c r="Y191" t="inlineStr"/>
-      <c r="Z191" t="inlineStr"/>
-      <c r="AA191" t="inlineStr"/>
-      <c r="AB191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>MIR-191</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Gold 6530</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
-        <v>2</v>
-      </c>
-      <c r="D192" t="n">
-        <v>32</v>
-      </c>
-      <c r="E192" t="n">
-        <v>128</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2×480 ГБ SSD + 2×2000 ГБ SSD</t>
-        </is>
-      </c>
-      <c r="G192" t="n">
-        <v>60878</v>
-      </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
-      <c r="T192" t="inlineStr"/>
-      <c r="U192" t="inlineStr"/>
-      <c r="V192" t="inlineStr"/>
-      <c r="W192" t="inlineStr"/>
-      <c r="X192" t="inlineStr"/>
-      <c r="Y192" t="inlineStr"/>
-      <c r="Z192" t="inlineStr"/>
-      <c r="AA192" t="inlineStr"/>
-      <c r="AB192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>MIR-192</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Gold 6530</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>2</v>
-      </c>
-      <c r="D193" t="n">
-        <v>32</v>
-      </c>
-      <c r="E193" t="n">
-        <v>192</v>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2×1000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G193" t="n">
-        <v>59780</v>
-      </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
-      <c r="R193" t="inlineStr"/>
-      <c r="S193" t="inlineStr"/>
-      <c r="T193" t="inlineStr"/>
-      <c r="U193" t="inlineStr"/>
-      <c r="V193" t="inlineStr"/>
-      <c r="W193" t="inlineStr"/>
-      <c r="X193" t="inlineStr"/>
-      <c r="Y193" t="inlineStr"/>
-      <c r="Z193" t="inlineStr"/>
-      <c r="AA193" t="inlineStr"/>
-      <c r="AB193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>MIR-193</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Gold 6530</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
-        <v>2</v>
-      </c>
-      <c r="D194" t="n">
-        <v>32</v>
-      </c>
-      <c r="E194" t="n">
-        <v>256</v>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2×2000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G194" t="n">
-        <v>62830</v>
-      </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
-      <c r="R194" t="inlineStr"/>
-      <c r="S194" t="inlineStr"/>
-      <c r="T194" t="inlineStr"/>
-      <c r="U194" t="inlineStr"/>
-      <c r="V194" t="inlineStr"/>
-      <c r="W194" t="inlineStr"/>
-      <c r="X194" t="inlineStr"/>
-      <c r="Y194" t="inlineStr"/>
-      <c r="Z194" t="inlineStr"/>
-      <c r="AA194" t="inlineStr"/>
-      <c r="AB194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>MIR-194</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Gold 6530</t>
-        </is>
-      </c>
-      <c r="C195" t="n">
-        <v>2</v>
-      </c>
-      <c r="D195" t="n">
-        <v>32</v>
-      </c>
-      <c r="E195" t="n">
-        <v>384</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2×4000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G195" t="n">
-        <v>68808</v>
-      </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
-      <c r="R195" t="inlineStr"/>
-      <c r="S195" t="inlineStr"/>
-      <c r="T195" t="inlineStr"/>
-      <c r="U195" t="inlineStr"/>
-      <c r="V195" t="inlineStr"/>
-      <c r="W195" t="inlineStr"/>
-      <c r="X195" t="inlineStr"/>
-      <c r="Y195" t="inlineStr"/>
-      <c r="Z195" t="inlineStr"/>
-      <c r="AA195" t="inlineStr"/>
-      <c r="AB195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>MIR-195</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Gold 6530</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
-        <v>2</v>
-      </c>
-      <c r="D196" t="n">
-        <v>32</v>
-      </c>
-      <c r="E196" t="n">
-        <v>768</v>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2×8000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G196" t="n">
-        <v>81374</v>
-      </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
-      <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr"/>
-      <c r="T196" t="inlineStr"/>
-      <c r="U196" t="inlineStr"/>
-      <c r="V196" t="inlineStr"/>
-      <c r="W196" t="inlineStr"/>
-      <c r="X196" t="inlineStr"/>
-      <c r="Y196" t="inlineStr"/>
-      <c r="Z196" t="inlineStr"/>
-      <c r="AA196" t="inlineStr"/>
-      <c r="AB196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>MIR-196</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Gold 6538Y</t>
-        </is>
-      </c>
-      <c r="C197" t="n">
-        <v>2</v>
-      </c>
-      <c r="D197" t="n">
-        <v>32</v>
-      </c>
-      <c r="E197" t="n">
-        <v>128</v>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2×2000 ГБ NVMe</t>
-        </is>
-      </c>
-      <c r="G197" t="n">
-        <v>116998</v>
-      </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
-      <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr"/>
-      <c r="T197" t="inlineStr"/>
-      <c r="U197" t="inlineStr"/>
-      <c r="V197" t="inlineStr"/>
-      <c r="W197" t="inlineStr"/>
-      <c r="X197" t="inlineStr"/>
-      <c r="Y197" t="inlineStr"/>
-      <c r="Z197" t="inlineStr"/>
-      <c r="AA197" t="inlineStr"/>
-      <c r="AB197" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
